--- a/satisfaction_surveys/015_sports_event_catering_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/015_sports_event_catering_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'food_quality'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'Food Quality'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'food_variety'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'Food Variety'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'food_presentation'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'Food Presentation'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'food_taste'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'Food Taste'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'food_value'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'Food Value'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'beverages_variety'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'Beverages Variety'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'beverages_availability'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'Beverages Availability'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'beverages_quality'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'Beverages Quality'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'beverages_value'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'Beverages Value'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'service_friendliness'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'Service Friendliness'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'service_efficiency'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'Service Efficiency'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'service_quality'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'Service Quality'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'service_value'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 'Service Value'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 'Very Satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 'Somewhat Satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'neutral'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 'Neutral'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'somewhat_dissatisfied'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 'Somewhat Dissatisfied'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'very_dissatisfied'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 'Very Dissatisfied'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'no_phone_number'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 'No Phone Number'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'phone_number'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 'Phone Number'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
